--- a/Challenge_1_Titanic/challenge1_titanic_TranHoMinhHai_3123410092/minh_chung_code/version_1_(16-09-2025)/process.xlsx
+++ b/Challenge_1_Titanic/challenge1_titanic_TranHoMinhHai_3123410092/minh_chung_code/version_1_(16-09-2025)/process.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dai_hoc\nam3\HK5\ML\LAB_GROUP\Challenge_1_Titanic\challenge1_titanic_TranHoMinhHai_3123410092\minh_chung_code\version_1_(16-09-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A33FA49-55D3-4856-B15D-9C03BCB3881D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E72EFE-B10A-4A36-9033-65D7934AB5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="16-09-2025" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="94">
   <si>
     <t>Xử lý missing value</t>
   </si>
@@ -316,6 +316,12 @@
   </si>
   <si>
     <t>0.8604</t>
+  </si>
+  <si>
+    <t>map (male: 0, female: 1)</t>
+  </si>
+  <si>
+    <t>map (S: 1, Q: 2, C: 3)</t>
   </si>
 </sst>
 </file>
@@ -441,10 +447,17 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -456,13 +469,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -758,172 +764,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="5"/>
+      <c r="D1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="4"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
+      <c r="B10" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>17</v>
+      <c r="B13" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -951,188 +957,188 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="5"/>
+      <c r="D1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="4"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="21" x14ac:dyDescent="0.3">
-      <c r="B18" s="7"/>
+      <c r="B18" s="3"/>
     </row>
     <row r="19" spans="1:2" ht="21" x14ac:dyDescent="0.4">
-      <c r="B19" s="8"/>
+      <c r="B19" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1158,180 +1164,180 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="5"/>
+      <c r="D1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="4"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="21" x14ac:dyDescent="0.3">
-      <c r="B17" s="7"/>
+      <c r="B17" s="3"/>
     </row>
     <row r="18" spans="2:2" ht="21" x14ac:dyDescent="0.4">
-      <c r="B18" s="8"/>
+      <c r="B18" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1357,212 +1363,212 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="5"/>
+      <c r="D1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="4"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="4"/>
+      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="2" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1601,220 +1607,220 @@
       <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="D2" s="3" t="s">
+      <c r="B2" s="5"/>
+      <c r="D2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="4"/>
+      <c r="B9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="2" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1830,220 +1836,220 @@
       <c r="G25" s="9"/>
     </row>
     <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="D26" s="3" t="s">
+      <c r="B26" s="5"/>
+      <c r="D26" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="4"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="4"/>
+      <c r="B33" s="7"/>
     </row>
     <row r="34" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>76</v>
       </c>
     </row>
